--- a/InputData/elec/BBNPPTY/BAU Ban New Power Plants This Year.xlsx
+++ b/InputData/elec/BBNPPTY/BAU Ban New Power Plants This Year.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Models\US\Models\eps-us\InputData\elec\BBNPPTY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\BBNPPTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED5C7C3-C6DD-4CC0-A75D-D5DA17DC76DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{385F7B4F-2A1E-47AD-ABA4-C02D7972106A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3900" windowWidth="38865" windowHeight="17235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>Source:</t>
   </si>
@@ -134,13 +134,34 @@
     <t>This is a Boolean value that should be set to 0 or 1 in each year.</t>
   </si>
   <si>
-    <t>In the U.S., we use this to represent EPA 111 Rules. New coal without CCS is banned starting in</t>
-  </si>
-  <si>
-    <t>We also assume no new coal with CCS can be built prior to 2028 given the state of the technology</t>
-  </si>
-  <si>
     <t>and the construction time for new or modified plants.</t>
+  </si>
+  <si>
+    <t>Due to recent blocks on offshore wind permitting and leasing, we assume only</t>
+  </si>
+  <si>
+    <t>already planned capacity (captured in elec/BPMCCS) will be built, and other</t>
+  </si>
+  <si>
+    <t>economic or reliability additions will not occur (offshore wind set to 1 in this file).</t>
+  </si>
+  <si>
+    <t>For historical years (2021-2024), we directly read in capacity additions in other input</t>
+  </si>
+  <si>
+    <t>data files and therefore disallow additional economic additions.</t>
+  </si>
+  <si>
+    <t>Conventional nuclear plants have an especially long lead time, so we default to the NEMS assumption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">that these plants have a 6 year lead time and therefore cannot be built for economic reasons before 2031 </t>
+  </si>
+  <si>
+    <t>(planned additions according to EIA are included in elec/BPMCCS)</t>
+  </si>
+  <si>
+    <t>We also assume no new coal with CCS or hydrogen can be built prior to 2028 given the state of the technology</t>
   </si>
 </sst>
 </file>
@@ -523,18 +544,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="60.85546875" customWidth="1"/>
+    <col min="2" max="2" width="60.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -542,54 +563,84 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" s="3">
         <v>2024</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>2028</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -604,13 +655,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="1" max="1" width="26.453125" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -705,7 +756,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -718,8 +769,8 @@
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" s="5">
-        <v>0</v>
+      <c r="E2">
+        <v>1</v>
       </c>
       <c r="F2" s="5">
         <v>0</v>
@@ -731,76 +782,76 @@
         <v>0</v>
       </c>
       <c r="I2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -813,8 +864,8 @@
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3" s="5">
-        <v>0</v>
+      <c r="E3">
+        <v>1</v>
       </c>
       <c r="F3" s="5">
         <v>0</v>
@@ -895,7 +946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -908,8 +959,8 @@
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" s="5">
-        <v>0</v>
+      <c r="E4">
+        <v>1</v>
       </c>
       <c r="F4" s="5">
         <v>0</v>
@@ -990,7 +1041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1003,26 +1054,26 @@
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" s="5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
       </c>
       <c r="L5" s="5">
         <v>0</v>
@@ -1085,7 +1136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -1098,8 +1149,8 @@
       <c r="D6">
         <v>1</v>
       </c>
-      <c r="E6" s="5">
-        <v>0</v>
+      <c r="E6">
+        <v>1</v>
       </c>
       <c r="F6" s="5">
         <v>0</v>
@@ -1180,7 +1231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1193,8 +1244,8 @@
       <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7" s="5">
-        <v>0</v>
+      <c r="E7">
+        <v>1</v>
       </c>
       <c r="F7" s="5">
         <v>0</v>
@@ -1275,7 +1326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1288,8 +1339,8 @@
       <c r="D8">
         <v>1</v>
       </c>
-      <c r="E8" s="5">
-        <v>0</v>
+      <c r="E8">
+        <v>1</v>
       </c>
       <c r="F8" s="5">
         <v>0</v>
@@ -1370,7 +1421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1383,8 +1434,8 @@
       <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9" s="5">
-        <v>0</v>
+      <c r="E9">
+        <v>1</v>
       </c>
       <c r="F9" s="5">
         <v>0</v>
@@ -1465,7 +1516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -1478,8 +1529,8 @@
       <c r="D10">
         <v>1</v>
       </c>
-      <c r="E10" s="5">
-        <v>0</v>
+      <c r="E10">
+        <v>1</v>
       </c>
       <c r="F10" s="5">
         <v>0</v>
@@ -1560,7 +1611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -1573,8 +1624,8 @@
       <c r="D11">
         <v>1</v>
       </c>
-      <c r="E11" s="5">
-        <v>0</v>
+      <c r="E11">
+        <v>1</v>
       </c>
       <c r="F11" s="5">
         <v>0</v>
@@ -1655,7 +1706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -1668,8 +1719,8 @@
       <c r="D12">
         <v>1</v>
       </c>
-      <c r="E12" s="5">
-        <v>0</v>
+      <c r="E12">
+        <v>1</v>
       </c>
       <c r="F12" s="5">
         <v>0</v>
@@ -1750,7 +1801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1763,8 +1814,8 @@
       <c r="D13">
         <v>1</v>
       </c>
-      <c r="E13" s="5">
-        <v>0</v>
+      <c r="E13">
+        <v>1</v>
       </c>
       <c r="F13" s="5">
         <v>0</v>
@@ -1845,7 +1896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1858,8 +1909,8 @@
       <c r="D14">
         <v>1</v>
       </c>
-      <c r="E14" s="5">
-        <v>0</v>
+      <c r="E14">
+        <v>1</v>
       </c>
       <c r="F14" s="5">
         <v>0</v>
@@ -1871,76 +1922,76 @@
         <v>0</v>
       </c>
       <c r="I14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE14" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1953,89 +2004,89 @@
       <c r="D15">
         <v>1</v>
       </c>
-      <c r="E15" s="5">
-        <v>0</v>
-      </c>
-      <c r="F15" s="5">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5">
-        <v>0</v>
-      </c>
-      <c r="H15" s="5">
-        <v>0</v>
-      </c>
-      <c r="I15" s="5">
-        <v>0</v>
-      </c>
-      <c r="J15" s="5">
-        <v>0</v>
-      </c>
-      <c r="K15" s="5">
-        <v>0</v>
-      </c>
-      <c r="L15" s="5">
-        <v>0</v>
-      </c>
-      <c r="M15" s="5">
-        <v>0</v>
-      </c>
-      <c r="N15" s="5">
-        <v>0</v>
-      </c>
-      <c r="O15" s="5">
-        <v>0</v>
-      </c>
-      <c r="P15" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="5">
-        <v>0</v>
-      </c>
-      <c r="R15" s="5">
-        <v>0</v>
-      </c>
-      <c r="S15" s="5">
-        <v>0</v>
-      </c>
-      <c r="T15" s="5">
-        <v>0</v>
-      </c>
-      <c r="U15" s="5">
-        <v>0</v>
-      </c>
-      <c r="V15" s="5">
-        <v>0</v>
-      </c>
-      <c r="W15" s="5">
-        <v>0</v>
-      </c>
-      <c r="X15" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+      <c r="W15">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>1</v>
+      </c>
+      <c r="Y15">
+        <v>1</v>
+      </c>
+      <c r="Z15">
+        <v>1</v>
+      </c>
+      <c r="AA15">
+        <v>1</v>
+      </c>
+      <c r="AB15">
+        <v>1</v>
+      </c>
+      <c r="AC15">
+        <v>1</v>
+      </c>
+      <c r="AD15">
+        <v>1</v>
+      </c>
+      <c r="AE15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -2048,8 +2099,8 @@
       <c r="D16">
         <v>1</v>
       </c>
-      <c r="E16" s="5">
-        <v>0</v>
+      <c r="E16">
+        <v>1</v>
       </c>
       <c r="F16" s="5">
         <v>0</v>
@@ -2130,7 +2181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -2143,8 +2194,8 @@
       <c r="D17">
         <v>1</v>
       </c>
-      <c r="E17" s="5">
-        <v>0</v>
+      <c r="E17">
+        <v>1</v>
       </c>
       <c r="F17" s="5">
         <v>0</v>
@@ -2225,7 +2276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -2238,8 +2289,8 @@
       <c r="D18">
         <v>1</v>
       </c>
-      <c r="E18" s="5">
-        <v>0</v>
+      <c r="E18">
+        <v>1</v>
       </c>
       <c r="F18" s="5">
         <v>0</v>
@@ -2320,7 +2371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -2333,7 +2384,7 @@
       <c r="D19">
         <v>1</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19">
         <v>1</v>
       </c>
       <c r="F19" s="5">
@@ -2415,7 +2466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -2428,7 +2479,7 @@
       <c r="D20">
         <v>1</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20">
         <v>1</v>
       </c>
       <c r="F20" s="5">
@@ -2510,7 +2561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -2523,7 +2574,7 @@
       <c r="D21">
         <v>1</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21">
         <v>1</v>
       </c>
       <c r="F21" s="5">
@@ -2605,7 +2656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -2618,7 +2669,7 @@
       <c r="D22">
         <v>1</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22">
         <v>1</v>
       </c>
       <c r="F22" s="5">
@@ -2700,7 +2751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -2713,17 +2764,17 @@
       <c r="D23">
         <v>1</v>
       </c>
-      <c r="E23" s="5">
-        <v>0</v>
+      <c r="E23">
+        <v>1</v>
       </c>
       <c r="F23" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="5">
         <v>0</v>
@@ -2795,7 +2846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>25</v>
       </c>
@@ -2808,17 +2859,17 @@
       <c r="D24">
         <v>1</v>
       </c>
-      <c r="E24" s="5">
-        <v>0</v>
+      <c r="E24">
+        <v>1</v>
       </c>
       <c r="F24" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="5">
         <v>0</v>
@@ -2890,7 +2941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
@@ -2903,17 +2954,17 @@
       <c r="D25">
         <v>1</v>
       </c>
-      <c r="E25" s="5">
-        <v>0</v>
+      <c r="E25">
+        <v>1</v>
       </c>
       <c r="F25" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="5">
         <v>0</v>

--- a/InputData/elec/BBNPPTY/BAU Ban New Power Plants This Year.xlsx
+++ b/InputData/elec/BBNPPTY/BAU Ban New Power Plants This Year.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\BBNPPTY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\elec\BBNPPTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{385F7B4F-2A1E-47AD-ABA4-C02D7972106A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D074A985-6CC5-4AEA-AF92-B01A9D3FF736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="62850" yWindow="1380" windowWidth="21600" windowHeight="12525" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Source:</t>
   </si>
@@ -134,6 +134,12 @@
     <t>This is a Boolean value that should be set to 0 or 1 in each year.</t>
   </si>
   <si>
+    <t>In the U.S., we use this to represent EPA 111 Rules. New coal without CCS is banned starting in</t>
+  </si>
+  <si>
+    <t>We also assume no new coal with CCS can be built prior to 2028 given the state of the technology</t>
+  </si>
+  <si>
     <t>and the construction time for new or modified plants.</t>
   </si>
   <si>
@@ -144,24 +150,6 @@
   </si>
   <si>
     <t>economic or reliability additions will not occur (offshore wind set to 1 in this file).</t>
-  </si>
-  <si>
-    <t>For historical years (2021-2024), we directly read in capacity additions in other input</t>
-  </si>
-  <si>
-    <t>data files and therefore disallow additional economic additions.</t>
-  </si>
-  <si>
-    <t>Conventional nuclear plants have an especially long lead time, so we default to the NEMS assumption</t>
-  </si>
-  <si>
-    <t xml:space="preserve">that these plants have a 6 year lead time and therefore cannot be built for economic reasons before 2031 </t>
-  </si>
-  <si>
-    <t>(planned additions according to EIA are included in elec/BPMCCS)</t>
-  </si>
-  <si>
-    <t>We also assume no new coal with CCS or hydrogen can be built prior to 2028 given the state of the technology</t>
   </si>
 </sst>
 </file>
@@ -544,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="60.81640625" customWidth="1"/>
@@ -595,12 +583,12 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>33</v>
+      <c r="A13">
+        <v>2028</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -613,8 +601,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>36</v>
       </c>
     </row>
@@ -626,21 +614,6 @@
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -769,7 +742,7 @@
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="5">
         <v>1</v>
       </c>
       <c r="F2" s="5">
@@ -782,73 +755,73 @@
         <v>0</v>
       </c>
       <c r="I2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.35">
@@ -864,7 +837,7 @@
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="5">
         <v>1</v>
       </c>
       <c r="F3" s="5">
@@ -959,7 +932,7 @@
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="5">
         <v>1</v>
       </c>
       <c r="F4" s="5">
@@ -1054,26 +1027,26 @@
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
       </c>
       <c r="L5" s="5">
         <v>0</v>
@@ -1149,7 +1122,7 @@
       <c r="D6">
         <v>1</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="5">
         <v>1</v>
       </c>
       <c r="F6" s="5">
@@ -1244,7 +1217,7 @@
       <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="5">
         <v>1</v>
       </c>
       <c r="F7" s="5">
@@ -1339,7 +1312,7 @@
       <c r="D8">
         <v>1</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="5">
         <v>1</v>
       </c>
       <c r="F8" s="5">
@@ -1434,7 +1407,7 @@
       <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="5">
         <v>1</v>
       </c>
       <c r="F9" s="5">
@@ -1529,7 +1502,7 @@
       <c r="D10">
         <v>1</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="5">
         <v>1</v>
       </c>
       <c r="F10" s="5">
@@ -1624,7 +1597,7 @@
       <c r="D11">
         <v>1</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="5">
         <v>1</v>
       </c>
       <c r="F11" s="5">
@@ -1719,7 +1692,7 @@
       <c r="D12">
         <v>1</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="5">
         <v>1</v>
       </c>
       <c r="F12" s="5">
@@ -1814,7 +1787,7 @@
       <c r="D13">
         <v>1</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="5">
         <v>1</v>
       </c>
       <c r="F13" s="5">
@@ -1909,7 +1882,7 @@
       <c r="D14">
         <v>1</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="5">
         <v>1</v>
       </c>
       <c r="F14" s="5">
@@ -1922,73 +1895,73 @@
         <v>0</v>
       </c>
       <c r="I14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.35">
@@ -2004,7 +1977,7 @@
       <c r="D15">
         <v>1</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="5">
         <v>1</v>
       </c>
       <c r="F15">
@@ -2099,7 +2072,7 @@
       <c r="D16">
         <v>1</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="5">
         <v>1</v>
       </c>
       <c r="F16" s="5">
@@ -2194,7 +2167,7 @@
       <c r="D17">
         <v>1</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="5">
         <v>1</v>
       </c>
       <c r="F17" s="5">
@@ -2289,7 +2262,7 @@
       <c r="D18">
         <v>1</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="5">
         <v>1</v>
       </c>
       <c r="F18" s="5">
@@ -2384,7 +2357,7 @@
       <c r="D19">
         <v>1</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="5">
         <v>1</v>
       </c>
       <c r="F19" s="5">
@@ -2479,7 +2452,7 @@
       <c r="D20">
         <v>1</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="5">
         <v>1</v>
       </c>
       <c r="F20" s="5">
@@ -2574,7 +2547,7 @@
       <c r="D21">
         <v>1</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="5">
         <v>1</v>
       </c>
       <c r="F21" s="5">
@@ -2669,7 +2642,7 @@
       <c r="D22">
         <v>1</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="5">
         <v>1</v>
       </c>
       <c r="F22" s="5">
@@ -2764,17 +2737,17 @@
       <c r="D23">
         <v>1</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="5">
         <v>1</v>
       </c>
       <c r="F23" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="5">
         <v>0</v>
@@ -2859,17 +2832,17 @@
       <c r="D24">
         <v>1</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="5">
         <v>1</v>
       </c>
       <c r="F24" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" s="5">
         <v>0</v>
@@ -2954,17 +2927,17 @@
       <c r="D25">
         <v>1</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="5">
         <v>1</v>
       </c>
       <c r="F25" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" s="5">
         <v>0</v>
